--- a/plantillas/90.xlsx
+++ b/plantillas/90.xlsx
@@ -13413,7 +13413,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -14073,7 +14073,7 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -14313,7 +14313,7 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -14353,7 +14353,7 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -14393,7 +14393,7 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -14553,7 +14553,7 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -14933,7 +14933,7 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -15273,7 +15273,7 @@
         </is>
       </c>
       <c r="C106" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -15893,7 +15893,7 @@
         </is>
       </c>
       <c r="C137" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16133,7 +16133,7 @@
         </is>
       </c>
       <c r="C149" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16153,7 +16153,7 @@
         </is>
       </c>
       <c r="C150" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -17173,7 +17173,7 @@
         </is>
       </c>
       <c r="C201" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -17193,7 +17193,7 @@
         </is>
       </c>
       <c r="C202" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -17653,7 +17653,7 @@
         </is>
       </c>
       <c r="C225" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -17793,7 +17793,7 @@
         </is>
       </c>
       <c r="C232" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -17873,7 +17873,7 @@
         </is>
       </c>
       <c r="C236" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -18013,7 +18013,7 @@
         </is>
       </c>
       <c r="C243" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -18273,7 +18273,7 @@
         </is>
       </c>
       <c r="C256" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -18293,7 +18293,7 @@
         </is>
       </c>
       <c r="C257" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -18753,7 +18753,7 @@
         </is>
       </c>
       <c r="C280" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18813,7 +18813,7 @@
         </is>
       </c>
       <c r="C283" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -19153,7 +19153,7 @@
         </is>
       </c>
       <c r="C300" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -20313,7 +20313,7 @@
         </is>
       </c>
       <c r="C358" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -20433,7 +20433,7 @@
         </is>
       </c>
       <c r="C364" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -20453,7 +20453,7 @@
         </is>
       </c>
       <c r="C365" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -20473,7 +20473,7 @@
         </is>
       </c>
       <c r="C366" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -20493,7 +20493,7 @@
         </is>
       </c>
       <c r="C367" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22033,7 +22033,7 @@
         </is>
       </c>
       <c r="C444" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -25213,7 +25213,7 @@
         </is>
       </c>
       <c r="C603" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -25453,7 +25453,7 @@
         </is>
       </c>
       <c r="C615" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -25853,7 +25853,7 @@
         </is>
       </c>
       <c r="C635" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -27253,7 +27253,7 @@
         </is>
       </c>
       <c r="C705" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -27393,7 +27393,7 @@
         </is>
       </c>
       <c r="C712" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -27513,7 +27513,7 @@
         </is>
       </c>
       <c r="C718" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -27553,7 +27553,7 @@
         </is>
       </c>
       <c r="C720" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -28273,7 +28273,7 @@
         </is>
       </c>
       <c r="C756" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -28531,7 +28531,7 @@
       </c>
       <c r="B771" t="inlineStr">
         <is>
-          <t>20.10.2026</t>
+          <t>21.10.2026</t>
         </is>
       </c>
     </row>
